--- a/current-software-2026-10-27/UAT_Templates/ZY_Path_UAT_Data_and_Scoring.xlsx
+++ b/current-software-2026-10-27/UAT_Templates/ZY_Path_UAT_Data_and_Scoring.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B3" s="3" t="inlineStr">
         <is>
-          <t>codex-ready-2026-10-15 @ 1f3e01e</t>
+          <t>Reference software revision3a935ef (Windows508passed); record the actual study version before collecting responses.</t>
         </is>
       </c>
     </row>
